--- a/wwwroot/UploadTemplate/MRP/SPOUploadTemplate.xlsx
+++ b/wwwroot/UploadTemplate/MRP/SPOUploadTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL-202100139\Desktop\MRP\UploadTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB651963-4F7C-4A02-A6BB-56D60CC66523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0BF977-070B-4F01-B9B8-47DEC3639A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{62A03AEE-7FE2-45F5-BDFC-C6C8AA458EBE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Model</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>UY701AV</t>
+  </si>
+  <si>
+    <t>PlanShipDt [yyyy/MM/dd]</t>
   </si>
 </sst>
 </file>
@@ -80,8 +83,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,26 +420,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58A770E1-9DF8-496B-9F76-EB60CD0045A6}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="23" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>2000</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46094</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>